--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0A03A20-572B-4334-A1FB-4E6CF7F66836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{884A7B32-2C7B-4F5A-AEA2-5CA42A1202A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{884A7B32-2C7B-4F5A-AEA2-5CA42A1202A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E04E768B-2A9D-416D-BFE7-70591F689900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="163">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -493,6 +493,12 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>w334825256-330</t>
+  </si>
+  <si>
+    <t>at grid node - w334825256-330</t>
+  </si>
+  <si>
     <t>w477596994-330</t>
   </si>
   <si>
@@ -521,18 +527,6 @@
   </si>
   <si>
     <t>at grid node - w1324578567-330</t>
-  </si>
-  <si>
-    <t>w1328602766-330</t>
-  </si>
-  <si>
-    <t>at grid node - w1328602766-330</t>
-  </si>
-  <si>
-    <t>NG20-330</t>
-  </si>
-  <si>
-    <t>at grid node - NG20-330</t>
   </si>
 </sst>
 </file>
@@ -1039,10 +1033,10 @@
         <v>78</v>
       </c>
       <c r="R12" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="S12" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="T12" t="s">
         <v>150</v>
@@ -1089,10 +1083,10 @@
         <v>78</v>
       </c>
       <c r="R13" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="S13" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="T13" t="s">
         <v>150</v>
@@ -1189,10 +1183,10 @@
         <v>78</v>
       </c>
       <c r="R15" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="S15" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="T15" t="s">
         <v>150</v>
@@ -1239,10 +1233,10 @@
         <v>78</v>
       </c>
       <c r="R16" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="S16" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="T16" t="s">
         <v>150</v>
@@ -1289,10 +1283,10 @@
         <v>78</v>
       </c>
       <c r="R17" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="S17" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="T17" t="s">
         <v>150</v>
@@ -1339,10 +1333,10 @@
         <v>78</v>
       </c>
       <c r="R18" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="S18" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="T18" t="s">
         <v>150</v>
@@ -1389,10 +1383,10 @@
         <v>78</v>
       </c>
       <c r="R19" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="S19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T19" t="s">
         <v>150</v>
@@ -1489,10 +1483,10 @@
         <v>78</v>
       </c>
       <c r="R21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="S21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="T21" t="s">
         <v>150</v>
@@ -1535,18 +1529,6 @@
       <c r="O22" t="s">
         <v>147</v>
       </c>
-      <c r="Q22" t="s">
-        <v>78</v>
-      </c>
-      <c r="R22" t="s">
-        <v>161</v>
-      </c>
-      <c r="S22" t="s">
-        <v>162</v>
-      </c>
-      <c r="T22" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
@@ -1573,18 +1555,6 @@
       <c r="O23" t="s">
         <v>147</v>
       </c>
-      <c r="Q23" t="s">
-        <v>78</v>
-      </c>
-      <c r="R23" t="s">
-        <v>124</v>
-      </c>
-      <c r="S23" t="s">
-        <v>125</v>
-      </c>
-      <c r="T23" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
@@ -1610,18 +1580,6 @@
       </c>
       <c r="O24" t="s">
         <v>147</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>78</v>
-      </c>
-      <c r="R24" t="s">
-        <v>163</v>
-      </c>
-      <c r="S24" t="s">
-        <v>164</v>
-      </c>
-      <c r="T24" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E04E768B-2A9D-416D-BFE7-70591F689900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE8038CD-2010-4665-AD40-D99C8E474856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE8038CD-2010-4665-AD40-D99C8E474856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09D9F12B-6A5A-40A5-B70A-81ABB390CEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09D9F12B-6A5A-40A5-B70A-81ABB390CEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37660F3A-758B-4ECF-B6E4-32B75FBAC564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37660F3A-758B-4ECF-B6E4-32B75FBAC564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E370487-FBF4-4914-B8EF-14F8594A20DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="172">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -263,6 +263,33 @@
   </si>
   <si>
     <t>ELC_wo*</t>
+  </si>
+  <si>
+    <t>pset_set</t>
+  </si>
+  <si>
+    <t>limtype</t>
+  </si>
+  <si>
+    <t>other_indexes</t>
+  </si>
+  <si>
+    <t>flo_emis</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>co2</t>
+  </si>
+  <si>
+    <t>co2captured</t>
+  </si>
+  <si>
+    <t>*ccs*</t>
+  </si>
+  <si>
+    <t>coal,oil,bioenergy</t>
   </si>
   <si>
     <t>~replicateinregions</t>
@@ -880,16 +907,16 @@
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="Q9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -897,10 +924,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -909,10 +936,10 @@
         <v>33</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J10" t="s">
         <v>21</v>
@@ -921,10 +948,10 @@
         <v>33</v>
       </c>
       <c r="M10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="N10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="O10" t="s">
         <v>21</v>
@@ -933,10 +960,10 @@
         <v>33</v>
       </c>
       <c r="R10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="S10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="T10" t="s">
         <v>21</v>
@@ -944,1042 +971,1042 @@
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I11" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J11" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M11" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="N11" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="O11" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R11" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="S11" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="T11" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="I12" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J12" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M12" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="N12" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="O12" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q12" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R12" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="S12" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="T12" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I13" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="J13" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M13" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="N13" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="O13" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R13" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="S13" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="T13" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I14" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J14" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M14" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="N14" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="O14" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q14" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R14" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="S14" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="T14" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I15" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="J15" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M15" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="N15" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O15" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R15" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="S15" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="T15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
         <v>90</v>
       </c>
-      <c r="D16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" t="s">
-        <v>81</v>
-      </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I16" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="J16" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M16" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N16" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O16" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R16" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="S16" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="T16" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" t="s">
+        <v>147</v>
+      </c>
+      <c r="J17" t="s">
         <v>137</v>
       </c>
-      <c r="I17" t="s">
-        <v>138</v>
-      </c>
-      <c r="J17" t="s">
-        <v>128</v>
-      </c>
       <c r="L17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="N17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O17" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R17" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="S17" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="T17" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I18" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" t="s">
+        <v>137</v>
+      </c>
+      <c r="L18" t="s">
+        <v>87</v>
+      </c>
+      <c r="M18" t="s">
+        <v>103</v>
+      </c>
+      <c r="N18" t="s">
+        <v>104</v>
+      </c>
+      <c r="O18" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>87</v>
+      </c>
+      <c r="R18" t="s">
         <v>140</v>
       </c>
-      <c r="J18" t="s">
-        <v>128</v>
-      </c>
-      <c r="L18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M18" t="s">
-        <v>94</v>
-      </c>
-      <c r="N18" t="s">
-        <v>95</v>
-      </c>
-      <c r="O18" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>78</v>
-      </c>
-      <c r="R18" t="s">
-        <v>131</v>
-      </c>
       <c r="S18" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="T18" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="I19" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="J19" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M19" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="O19" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q19" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R19" t="s">
+        <v>168</v>
+      </c>
+      <c r="S19" t="s">
+        <v>169</v>
+      </c>
+      <c r="T19" t="s">
         <v>159</v>
-      </c>
-      <c r="S19" t="s">
-        <v>160</v>
-      </c>
-      <c r="T19" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I20" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="J20" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L20" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M20" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="N20" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="O20" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q20" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R20" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="S20" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="T20" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="I21" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="J21" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L21" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M21" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="N21" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="O21" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="Q21" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="R21" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="S21" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="T21" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I22" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J22" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L22" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M22" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N22" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="O22" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M23" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="N23" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="O23" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L24" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M24" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="N24" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="O24" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L25" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M25" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="N25" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="O25" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M26" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="N26" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="O26" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M27" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N27" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="O27" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L28" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M28" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="N28" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="O28" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L29" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M29" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="N29" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="O29" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L30" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M30" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="N30" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="O30" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L31" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M31" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N31" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="O31" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E32" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L32" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M32" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="N32" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="O32" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L33" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M33" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="N33" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="O33" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E34" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L34" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M34" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="N34" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="O34" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L35" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M35" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="N35" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="O35" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L36" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M36" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="N36" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O36" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L37" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M37" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="N37" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="O37" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L38" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M38" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="N38" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="O38" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L39" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M39" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="N39" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="O39" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L40" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M40" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N40" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="O40" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L41" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M41" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="N41" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="O41" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L42" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M42" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="N42" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="O42" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L43" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M43" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="N43" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="O43" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L44" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="M44" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="N44" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="O44" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -2625,7 +2652,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C4:X50"/>
+  <dimension ref="C4:X57"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
@@ -3376,7 +3403,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C49" t="s">
         <v>64</v>
       </c>
@@ -3390,7 +3417,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C50" t="s">
         <v>69</v>
       </c>
@@ -3402,6 +3429,86 @@
       </c>
       <c r="F50" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C55" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" t="s">
+        <v>65</v>
+      </c>
+      <c r="F55" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55" t="s">
+        <v>66</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>2022</v>
+      </c>
+      <c r="J55">
+        <v>2030</v>
+      </c>
+      <c r="K55" t="s">
+        <v>76</v>
+      </c>
+      <c r="L55" t="s">
+        <v>77</v>
+      </c>
+      <c r="M55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56" t="s">
+        <v>82</v>
+      </c>
+      <c r="I56">
+        <v>0.95</v>
+      </c>
+      <c r="L56" t="s">
+        <v>80</v>
+      </c>
+      <c r="M56" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" t="s">
+        <v>83</v>
+      </c>
+      <c r="F57" t="s">
+        <v>82</v>
+      </c>
+      <c r="I57">
+        <v>0.85</v>
+      </c>
+      <c r="L57" t="s">
+        <v>80</v>
+      </c>
+      <c r="M57" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
